--- a/EKG_Kalite_Yönetim_Sistemi/98_Uygulama_Kayıtları/02_Proje ve Ürün-Proses Yeterliliği/EKG-PRJ-FRM-24_is_akis_semasi__ske_metal_proses_ornegi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/98_Uygulama_Kayıtları/02_Proje ve Ürün-Proses Yeterliliği/EKG-PRJ-FRM-24_is_akis_semasi__ske_metal_proses_ornegi.xlsx
@@ -6172,7 +6172,8 @@
   <pageSetup paperSize="8" scale="37" orientation="portrait" r:id="rId1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-24&amp;C&amp;"Arial,Regular"&amp;11İş Akış Şeması - SKE Metal Proses Örneği</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 28.09.2026
+Revizyon nedeni: SKE/metal proses örneği açıkça işaretlendi; kaynak akış ve tarih korundu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
